--- a/data/site_level_data_site_comments_added.xlsx
+++ b/data/site_level_data_site_comments_added.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ad.helsinki.fi\home\l\laakjuha\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Baltica_conmpilation_manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83A7F370-45A9-431D-B2A7-0F38C3B80A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5036C9-BBF7-46D4-8550-CC4D1B465797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="70" activeTab="71" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="70" activeTab="53" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mean D Burakovskaya intrusion a" sheetId="77" r:id="rId1"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3655" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3667" uniqueCount="1069">
   <si>
     <t>–</t>
   </si>
@@ -3309,6 +3309,12 @@
   </si>
   <si>
     <t>need check</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Pisarevsky &amp; Bylund (2010)</t>
   </si>
 </sst>
 </file>
@@ -3319,7 +3325,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="000.0"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3558,6 +3564,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -3707,7 +3718,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3953,19 +3964,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4349,7 +4353,7 @@
       <c r="H6" s="78">
         <v>224</v>
       </c>
-      <c r="I6" s="123" t="s">
+      <c r="I6" s="119" t="s">
         <v>1064</v>
       </c>
       <c r="Q6"/>
@@ -35764,7 +35768,7 @@
       <c r="H2" s="68">
         <v>186.93409928239612</v>
       </c>
-      <c r="I2" s="124" t="s">
+      <c r="I2" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35791,7 +35795,7 @@
       <c r="H3" s="68">
         <v>213.9773480293228</v>
       </c>
-      <c r="I3" s="124" t="s">
+      <c r="I3" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35818,7 +35822,7 @@
       <c r="H4" s="68">
         <v>212.39825022075783</v>
       </c>
-      <c r="I4" s="124" t="s">
+      <c r="I4" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35845,7 +35849,7 @@
       <c r="H5" s="68">
         <v>225.32609734879659</v>
       </c>
-      <c r="I5" s="124" t="s">
+      <c r="I5" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35874,7 +35878,7 @@
       <c r="H6" s="18">
         <v>189.9</v>
       </c>
-      <c r="I6" s="124" t="s">
+      <c r="I6" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35897,7 +35901,7 @@
       <c r="H7" s="18">
         <v>170.5</v>
       </c>
-      <c r="I7" s="124" t="s">
+      <c r="I7" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35926,7 +35930,7 @@
       <c r="H8" s="18">
         <v>219.9</v>
       </c>
-      <c r="I8" s="124" t="s">
+      <c r="I8" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35949,7 +35953,7 @@
       <c r="H9" s="18">
         <v>169</v>
       </c>
-      <c r="I9" s="124" t="s">
+      <c r="I9" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -35978,7 +35982,7 @@
       <c r="H10" s="18">
         <v>179.3</v>
       </c>
-      <c r="I10" s="124" t="s">
+      <c r="I10" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -36007,7 +36011,7 @@
       <c r="H11" s="18">
         <v>240.8</v>
       </c>
-      <c r="I11" s="124" t="s">
+      <c r="I11" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -36030,7 +36034,7 @@
       <c r="H12" s="18">
         <v>237.1</v>
       </c>
-      <c r="I12" s="124" t="s">
+      <c r="I12" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -36059,7 +36063,7 @@
       <c r="H13" s="18">
         <v>238.5</v>
       </c>
-      <c r="I13" s="124" t="s">
+      <c r="I13" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -36088,7 +36092,7 @@
       <c r="H14" s="18">
         <v>216.3</v>
       </c>
-      <c r="I14" s="124" t="s">
+      <c r="I14" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -36117,7 +36121,7 @@
       <c r="H15" s="18">
         <v>216.7</v>
       </c>
-      <c r="I15" s="124" t="s">
+      <c r="I15" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -36146,7 +36150,7 @@
       <c r="H16" s="18">
         <v>215.9</v>
       </c>
-      <c r="I16" s="124" t="s">
+      <c r="I16" s="120" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -37798,286 +37802,285 @@
         <v>124.22312042648012</v>
       </c>
     </row>
-    <row r="42" spans="1:8" s="119" customFormat="1"/>
-    <row r="43" spans="1:8" s="119" customFormat="1">
-      <c r="B43" s="120"/>
-      <c r="C43" s="121"/>
-      <c r="D43" s="121"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="122"/>
-      <c r="G43" s="121"/>
-    </row>
-    <row r="44" spans="1:8" s="119" customFormat="1">
-      <c r="B44" s="120"/>
-      <c r="C44" s="121"/>
-      <c r="D44" s="121"/>
-      <c r="E44" s="121"/>
-      <c r="F44" s="122"/>
-      <c r="G44" s="121"/>
-    </row>
-    <row r="45" spans="1:8" s="119" customFormat="1">
-      <c r="B45" s="120"/>
-      <c r="C45" s="121"/>
-      <c r="D45" s="121"/>
-      <c r="E45" s="121"/>
-      <c r="F45" s="122"/>
-      <c r="G45" s="121"/>
-    </row>
-    <row r="46" spans="1:8" s="119" customFormat="1">
-      <c r="B46" s="120"/>
-      <c r="C46" s="121"/>
-      <c r="D46" s="121"/>
-      <c r="E46" s="121"/>
-      <c r="F46" s="122"/>
-      <c r="G46" s="121"/>
-    </row>
-    <row r="47" spans="1:8" s="119" customFormat="1">
-      <c r="B47" s="120"/>
-      <c r="C47" s="121"/>
-      <c r="D47" s="121"/>
-      <c r="E47" s="121"/>
-      <c r="F47" s="122"/>
-      <c r="G47" s="121"/>
-    </row>
-    <row r="48" spans="1:8" s="119" customFormat="1">
-      <c r="B48" s="120"/>
-      <c r="C48" s="121"/>
-      <c r="D48" s="121"/>
-      <c r="E48" s="121"/>
-      <c r="F48" s="122"/>
-      <c r="G48" s="121"/>
-    </row>
-    <row r="49" spans="2:7" s="119" customFormat="1">
-      <c r="B49" s="120"/>
-      <c r="C49" s="121"/>
-      <c r="D49" s="121"/>
-      <c r="E49" s="121"/>
-      <c r="F49" s="122"/>
-      <c r="G49" s="121"/>
-    </row>
-    <row r="50" spans="2:7" s="119" customFormat="1">
-      <c r="B50" s="120"/>
-      <c r="C50" s="121"/>
-      <c r="D50" s="121"/>
-      <c r="E50" s="121"/>
-      <c r="F50" s="122"/>
-      <c r="G50" s="121"/>
-    </row>
-    <row r="51" spans="2:7" s="119" customFormat="1">
-      <c r="B51" s="120"/>
-      <c r="C51" s="121"/>
-      <c r="D51" s="121"/>
-      <c r="E51" s="121"/>
-      <c r="F51" s="122"/>
-      <c r="G51" s="121"/>
-    </row>
-    <row r="52" spans="2:7" s="119" customFormat="1">
-      <c r="B52" s="120"/>
-      <c r="C52" s="121"/>
-      <c r="D52" s="121"/>
-      <c r="E52" s="121"/>
-      <c r="F52" s="122"/>
-      <c r="G52" s="121"/>
-    </row>
-    <row r="53" spans="2:7" s="119" customFormat="1">
-      <c r="B53" s="120"/>
-      <c r="C53" s="121"/>
-      <c r="D53" s="121"/>
-      <c r="E53" s="121"/>
-      <c r="F53" s="122"/>
-      <c r="G53" s="121"/>
-    </row>
-    <row r="54" spans="2:7" s="119" customFormat="1">
-      <c r="B54" s="120"/>
-      <c r="C54" s="121"/>
-      <c r="D54" s="121"/>
-      <c r="E54" s="121"/>
-      <c r="F54" s="122"/>
-      <c r="G54" s="121"/>
-    </row>
-    <row r="55" spans="2:7" s="119" customFormat="1">
-      <c r="B55" s="120"/>
-      <c r="C55" s="121"/>
-      <c r="D55" s="121"/>
-      <c r="E55" s="121"/>
-      <c r="F55" s="122"/>
-      <c r="G55" s="121"/>
-    </row>
-    <row r="56" spans="2:7" s="119" customFormat="1">
-      <c r="B56" s="120"/>
-      <c r="C56" s="121"/>
-      <c r="D56" s="121"/>
-      <c r="E56" s="121"/>
-      <c r="F56" s="122"/>
-      <c r="G56" s="121"/>
-    </row>
-    <row r="57" spans="2:7" s="119" customFormat="1">
-      <c r="B57" s="120"/>
-      <c r="C57" s="121"/>
-      <c r="D57" s="121"/>
-      <c r="E57" s="121"/>
-      <c r="F57" s="122"/>
-      <c r="G57" s="121"/>
-    </row>
-    <row r="58" spans="2:7" s="119" customFormat="1">
-      <c r="B58" s="120"/>
-      <c r="C58" s="121"/>
-      <c r="D58" s="121"/>
-      <c r="E58" s="121"/>
-      <c r="F58" s="122"/>
-      <c r="G58" s="121"/>
-    </row>
-    <row r="59" spans="2:7" s="119" customFormat="1">
-      <c r="B59" s="120"/>
-      <c r="C59" s="121"/>
-      <c r="D59" s="121"/>
-      <c r="E59" s="121"/>
-      <c r="F59" s="122"/>
-      <c r="G59" s="121"/>
-    </row>
-    <row r="60" spans="2:7" s="119" customFormat="1">
-      <c r="B60" s="120"/>
-      <c r="C60" s="121"/>
-      <c r="D60" s="121"/>
-      <c r="E60" s="121"/>
-      <c r="F60" s="122"/>
-      <c r="G60" s="121"/>
-    </row>
-    <row r="61" spans="2:7" s="119" customFormat="1">
-      <c r="B61" s="120"/>
-      <c r="C61" s="121"/>
-      <c r="D61" s="121"/>
-      <c r="E61" s="121"/>
-      <c r="F61" s="122"/>
-      <c r="G61" s="121"/>
-    </row>
-    <row r="62" spans="2:7" s="119" customFormat="1">
-      <c r="B62" s="120"/>
-      <c r="C62" s="121"/>
-      <c r="D62" s="121"/>
-      <c r="E62" s="121"/>
-      <c r="F62" s="122"/>
-      <c r="G62" s="121"/>
-    </row>
-    <row r="63" spans="2:7" s="119" customFormat="1">
-      <c r="B63" s="120"/>
-      <c r="C63" s="121"/>
-      <c r="D63" s="121"/>
-      <c r="E63" s="121"/>
-      <c r="F63" s="122"/>
-      <c r="G63" s="121"/>
-    </row>
-    <row r="64" spans="2:7" s="119" customFormat="1">
-      <c r="B64" s="120"/>
-      <c r="C64" s="121"/>
-      <c r="D64" s="121"/>
-      <c r="E64" s="121"/>
-      <c r="F64" s="122"/>
-      <c r="G64" s="121"/>
-    </row>
-    <row r="65" spans="2:7" s="119" customFormat="1">
-      <c r="B65" s="120"/>
-      <c r="C65" s="121"/>
-      <c r="D65" s="121"/>
-      <c r="E65" s="121"/>
-      <c r="F65" s="122"/>
-      <c r="G65" s="121"/>
-    </row>
-    <row r="66" spans="2:7" s="119" customFormat="1">
-      <c r="B66" s="120"/>
-      <c r="C66" s="121"/>
-      <c r="D66" s="121"/>
-      <c r="E66" s="121"/>
-      <c r="F66" s="122"/>
-      <c r="G66" s="121"/>
-    </row>
-    <row r="67" spans="2:7" s="119" customFormat="1">
-      <c r="B67" s="120"/>
-      <c r="C67" s="121"/>
-      <c r="D67" s="121"/>
-      <c r="E67" s="121"/>
-      <c r="F67" s="122"/>
-      <c r="G67" s="121"/>
-    </row>
-    <row r="68" spans="2:7" s="119" customFormat="1">
-      <c r="B68" s="120"/>
-      <c r="C68" s="121"/>
-      <c r="D68" s="121"/>
-      <c r="E68" s="121"/>
-      <c r="F68" s="122"/>
-      <c r="G68" s="121"/>
-    </row>
-    <row r="69" spans="2:7" s="119" customFormat="1">
-      <c r="B69" s="120"/>
-      <c r="C69" s="121"/>
-      <c r="D69" s="121"/>
-      <c r="E69" s="121"/>
-      <c r="F69" s="122"/>
-      <c r="G69" s="121"/>
-    </row>
-    <row r="70" spans="2:7" s="119" customFormat="1">
-      <c r="B70" s="120"/>
-      <c r="C70" s="121"/>
-      <c r="D70" s="121"/>
-      <c r="E70" s="121"/>
-      <c r="F70" s="122"/>
-      <c r="G70" s="121"/>
-    </row>
-    <row r="71" spans="2:7" s="119" customFormat="1">
-      <c r="B71" s="120"/>
-      <c r="C71" s="121"/>
-      <c r="D71" s="121"/>
-      <c r="E71" s="121"/>
-      <c r="F71" s="122"/>
-      <c r="G71" s="121"/>
-    </row>
-    <row r="72" spans="2:7" s="119" customFormat="1">
-      <c r="B72" s="120"/>
-      <c r="C72" s="121"/>
-      <c r="D72" s="121"/>
-      <c r="E72" s="121"/>
-      <c r="F72" s="122"/>
-      <c r="G72" s="121"/>
-    </row>
-    <row r="73" spans="2:7" s="119" customFormat="1">
-      <c r="B73" s="120"/>
-      <c r="C73" s="121"/>
-      <c r="D73" s="121"/>
-      <c r="E73" s="121"/>
-      <c r="F73" s="122"/>
-      <c r="G73" s="121"/>
-    </row>
-    <row r="74" spans="2:7" s="119" customFormat="1">
-      <c r="B74" s="120"/>
-      <c r="C74" s="121"/>
-      <c r="D74" s="121"/>
-      <c r="E74" s="121"/>
-      <c r="F74" s="122"/>
-      <c r="G74" s="121"/>
-    </row>
-    <row r="75" spans="2:7" s="119" customFormat="1">
-      <c r="B75" s="120"/>
-      <c r="C75" s="121"/>
-      <c r="D75" s="121"/>
-      <c r="E75" s="121"/>
-      <c r="F75" s="122"/>
-      <c r="G75" s="121"/>
-    </row>
-    <row r="76" spans="2:7" s="119" customFormat="1">
-      <c r="B76" s="120"/>
-      <c r="C76" s="121"/>
-      <c r="D76" s="121"/>
-      <c r="E76" s="121"/>
-      <c r="F76" s="122"/>
-      <c r="G76" s="121"/>
-    </row>
-    <row r="77" spans="2:7" s="119" customFormat="1">
-      <c r="B77" s="120"/>
-      <c r="C77" s="121"/>
-      <c r="D77" s="121"/>
-      <c r="E77" s="121"/>
-      <c r="F77" s="122"/>
-      <c r="G77" s="121"/>
+    <row r="43" spans="1:8">
+      <c r="B43" s="16"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="B44" s="16"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="B45" s="16"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="22"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="B46" s="16"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="22"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="B47" s="16"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="22"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="B48" s="16"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="22"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="16"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="22"/>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="16"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="22"/>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="16"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="22"/>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="16"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="22"/>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="16"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="22"/>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="16"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="22"/>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="16"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="22"/>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="16"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="22"/>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="16"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="22"/>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="B58" s="16"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="22"/>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="B59" s="16"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="22"/>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="16"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="22"/>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="16"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="22"/>
+    </row>
+    <row r="62" spans="2:7">
+      <c r="B62" s="16"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="22"/>
+    </row>
+    <row r="63" spans="2:7">
+      <c r="B63" s="16"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="22"/>
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="16"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="22"/>
+    </row>
+    <row r="65" spans="2:7">
+      <c r="B65" s="16"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="22"/>
+    </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="16"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="22"/>
+    </row>
+    <row r="67" spans="2:7">
+      <c r="B67" s="16"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="22"/>
+    </row>
+    <row r="68" spans="2:7">
+      <c r="B68" s="16"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="22"/>
+    </row>
+    <row r="69" spans="2:7">
+      <c r="B69" s="16"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="22"/>
+    </row>
+    <row r="70" spans="2:7">
+      <c r="B70" s="16"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="22"/>
+    </row>
+    <row r="71" spans="2:7">
+      <c r="B71" s="16"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="22"/>
+    </row>
+    <row r="72" spans="2:7">
+      <c r="B72" s="16"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="22"/>
+    </row>
+    <row r="73" spans="2:7">
+      <c r="B73" s="16"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="22"/>
+    </row>
+    <row r="74" spans="2:7">
+      <c r="B74" s="16"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="22"/>
+    </row>
+    <row r="75" spans="2:7">
+      <c r="B75" s="16"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="22"/>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" s="16"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="22"/>
+    </row>
+    <row r="77" spans="2:7">
+      <c r="B77" s="16"/>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="22"/>
     </row>
     <row r="78" spans="2:7">
       <c r="B78" s="19"/>
@@ -39373,10 +39376,10 @@
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8B768A-71D3-40F2-80A1-E035610E593A}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="13">
+    <row r="1" spans="1:10" ht="13">
       <c r="A1" s="11" t="s">
         <v>1061</v>
       </c>
@@ -39404,8 +39407,11 @@
       <c r="I1" t="s">
         <v>1063</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="10" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
@@ -39430,8 +39436,11 @@
       <c r="H2">
         <v>158.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
@@ -39456,8 +39465,11 @@
       <c r="H3">
         <v>176.4</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
@@ -39482,8 +39494,11 @@
       <c r="H4">
         <v>169</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
@@ -39508,8 +39523,11 @@
       <c r="H5">
         <v>156</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>7</v>
       </c>
@@ -39534,8 +39552,11 @@
       <c r="H6">
         <v>194.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>8</v>
       </c>
@@ -39560,8 +39581,11 @@
       <c r="H7">
         <v>190.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>9</v>
       </c>
@@ -39586,8 +39610,11 @@
       <c r="H8">
         <v>178</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>10</v>
       </c>
@@ -39612,8 +39639,11 @@
       <c r="H9">
         <v>182.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>11</v>
       </c>
@@ -39638,8 +39668,11 @@
       <c r="H10">
         <v>186</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>14</v>
       </c>
@@ -39664,8 +39697,11 @@
       <c r="H11">
         <v>207.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="121" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>15</v>
       </c>
@@ -39689,6 +39725,9 @@
       </c>
       <c r="H12">
         <v>212.9</v>
+      </c>
+      <c r="J12" s="121" t="s">
+        <v>1068</v>
       </c>
     </row>
   </sheetData>
@@ -51838,21 +51877,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006B3CD0B4C4B1A149A44ADD94ADBD9DA3" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="67f7b35554696bef78661cc62203b5cf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6d503264-5df7-4f76-939a-a40fb8837487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="93ca4561670c9d1db5bf78b78de83361" ns2:_="">
     <xsd:import namespace="6d503264-5df7-4f76-939a-a40fb8837487"/>
@@ -51990,24 +52014,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99649137-85B4-4DC1-8336-96B96870CB30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBF11DBC-0ACB-43B2-B503-E97B4469979C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F934E6F5-D8D5-4D63-83CD-4EE5BC2281D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -52025,6 +52047,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99649137-85B4-4DC1-8336-96B96870CB30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBF11DBC-0ACB-43B2-B503-E97B4469979C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{98ae7559-10dc-4288-8e2e-4593e62fe3ee}" enabled="0" method="" siteId="{98ae7559-10dc-4288-8e2e-4593e62fe3ee}" removed="1"/>
